--- a/etf_holdings/2026-09-29_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:08</t>
+          <t>2026-09-29 01:02:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:10</t>
+          <t>2026-09-29 01:02:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:11</t>
+          <t>2026-09-29 01:02:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:12</t>
+          <t>2026-09-29 01:02:06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:12</t>
+          <t>2026-09-29 01:02:06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:12</t>
+          <t>2026-09-29 01:02:06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:12</t>
+          <t>2026-09-29 01:02:06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:12</t>
+          <t>2026-09-29 01:02:06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:12</t>
+          <t>2026-09-29 01:02:06</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:12</t>
+          <t>2026-09-29 01:02:06</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:12</t>
+          <t>2026-09-29 01:02:06</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">

--- a/etf_holdings/2026-09-29_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:02</t>
+          <t>2026-09-29 01:40:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:04</t>
+          <t>2026-09-29 01:40:57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:05</t>
+          <t>2026-09-29 01:40:58</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-29 01:02:06</t>
+          <t>2026-09-29 01:40:59</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">

--- a/etf_holdings/2026-09-29_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,20 +522,20 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.42%347,000</t>
+          <t>8.32%349,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.42%</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>347000</v>
+        <v>349000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5285</v>
+        <v>4910</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.60%131,000</t>
+          <t>6.70%131,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.60%</t>
+          <t>6.70%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,33 +631,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>-1.69%1165</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1185</v>
+        <v>1165</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.54%492,000</t>
+          <t>5.96%519,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>5.96%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>492000</v>
+        <v>519000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,33 +692,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3555</v>
+        <v>3400</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.33%158,000</t>
+          <t>5.65%164,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>5.65%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>158000</v>
+        <v>164000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,33 +753,33 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.67%8525</t>
+          <t>-7.04%7925</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-7.04%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8525</v>
+        <v>7925</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.29%65,000</t>
+          <t>5.45%66,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>5.45%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>65000</v>
+        <v>66000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,33 +814,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.88%100,000</t>
+          <t>4.94%101,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>100000</v>
+        <v>101000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>-0.71%2100</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.40%215,191</t>
+          <t>4.41%215,191</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.40%</t>
+          <t>4.41%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,33 +936,33 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5415</v>
+        <v>5185</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.37%80,000</t>
+          <t>4.30%82,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.37%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>80000</v>
+        <v>82000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.19%19835</t>
+          <t>-0.73%955</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>19835</v>
+        <v>955</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.06%20,600</t>
+          <t>4.01%431,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>20600</v>
+        <v>431000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+6.18%962</t>
+          <t>-2.22%19395</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+6.18%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>962</v>
+        <v>19395</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.77%428,000</t>
+          <t>3.96%20,600</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>428000</v>
+        <v>20600</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,20 +1119,20 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.33%503</t>
+          <t>+0.6%506</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.07%613,000</t>
+          <t>3.07%630,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1141,11 +1141,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>613000</v>
+        <v>630000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,29 +1180,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.48%1240</t>
+          <t>+2.42%1270</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.90%247,000</t>
+          <t>3.05%254,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>247000</v>
+        <v>254000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,33 +1241,33 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-3.75%154</t>
+          <t>-0.32%153.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>154</v>
+        <v>153.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.85%1,835,000</t>
+          <t>2.89%1,938,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1835000</v>
+        <v>1938000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.32%12350</t>
+          <t>-1.9%12115</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>12350</v>
+        <v>12115</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.41%20,000</t>
+          <t>2.39%20,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:55</t>
+          <t>2026-09-29 22:56:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>-4.49%1810</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1895</v>
+        <v>1810</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>-0.67%1485</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1495</v>
+        <v>1485</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.25%159,000</t>
+          <t>2.30%159,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,34 +1480,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.58%171.5</t>
+          <t>-0.36%6895</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>171.5</v>
+        <v>6895</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.06%1,228,000</t>
+          <t>2.28%34,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1228000</v>
+        <v>34000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,33 +1546,33 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+1.22%580</t>
+          <t>-5.52%548</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-5.52%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>580</v>
+        <v>548</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.03%365,000</t>
+          <t>2.18%388,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>365000</v>
+        <v>388000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>+1.46%174</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1910</v>
+        <v>174</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.99%108,000</t>
+          <t>2.06%1,238,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>108000</v>
+        <v>1238000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>-3.93%1835</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2340</v>
+        <v>1835</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.89%83,000</t>
+          <t>2.00%108,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>83000</v>
+        <v>108000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.36%554</t>
+          <t>+4.49%2445</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+4.49%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>554</v>
+        <v>2445</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.87%348,000</t>
+          <t>1.88%83,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>348000</v>
+        <v>83000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.89%6245</t>
+          <t>-1.99%543</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6245</v>
+        <v>543</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.56%26,000</t>
+          <t>1.87%348,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>26000</v>
+        <v>348000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+7.96%6920</t>
+          <t>-3.6%6020</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+7.96%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6920</v>
+        <v>6020</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.37%22,000</t>
+          <t>1.57%26,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>22000</v>
+        <v>26000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+4.62%238</t>
+          <t>+3.78%247</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+4.62%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.26%571,000</t>
+          <t>1.32%571,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.53%475.5</t>
+          <t>+4.84%498.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+4.84%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>475.5</v>
+        <v>498.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,33 +2034,33 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.68%971</t>
+          <t>-1.54%956</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.68%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>971</v>
+        <v>956</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.86%93,000</t>
+          <t>1.00%106,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>93000</v>
+        <v>106000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>3324雙鴻</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+2.82%511</t>
+          <t>-4.68%1630</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-4.68%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>511</v>
+        <v>1630</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.58%121,000</t>
+          <t>0.63%38,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>121000</v>
+        <v>38000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,34 +2151,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.69%2530</t>
+          <t>-2.54%498</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2530</v>
+        <v>498</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.56%22,000</t>
+          <t>0.60%121,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>22000</v>
+        <v>121000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3324雙鴻</t>
+          <t>2006東和鋼鐵</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+7.21%1710</t>
+          <t>-2.73%85.4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+7.21%</t>
+          <t>-2.73%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1710</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.54%35,000</t>
+          <t>0.59%699,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>35000</v>
+        <v>699000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:57</t>
+          <t>2026-09-29 22:56:35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,34 +2273,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2006東和鋼鐵</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.33%87.8</t>
+          <t>+1.11%730</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.33%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>87.8</v>
+        <v>730</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.52%628,000</t>
+          <t>0.59%84,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>628000</v>
+        <v>84000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+3%722</t>
+          <t>-1.72%687</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>722</v>
+        <v>687</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.52%76,000</t>
+          <t>0.58%85,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>76000</v>
+        <v>85000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>+4.2%620</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>699</v>
+        <v>620</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.51%76,000</t>
+          <t>0.55%95,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>76000</v>
+        <v>95000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+9.98%595</t>
+          <t>-0.59%2515</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>595</v>
+        <v>2515</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.50%95,000</t>
+          <t>0.54%22,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>95000</v>
+        <v>22000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2412中華電</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.75%2700</t>
+          <t>-0.69%144</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2700</v>
+        <v>144</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.49%19,000</t>
+          <t>0.50%357,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>19000</v>
+        <v>357000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2412中華電</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.34%145</t>
+          <t>-1.85%2650</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>145</v>
+        <v>2650</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.45%319,000</t>
+          <t>0.50%19,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>319000</v>
+        <v>19000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.43%465,000</t>
+          <t>0.43%474,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>465000</v>
+        <v>474000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,33 +2705,33 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0%76.7</t>
+          <t>-4.3%73.4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>76.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.33%446,000</t>
+          <t>0.37%498,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>446000</v>
+        <v>498000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3532台勝科</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.29%2295</t>
+          <t>+0.33%454</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2295</v>
+        <v>454</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.32%14,000</t>
+          <t>0.35%80,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>14000</v>
+        <v>80000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3532台勝科</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.69%452.5</t>
+          <t>-4.79%2185</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.69%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>452.5</v>
+        <v>2185</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.30%70,000</t>
+          <t>0.33%15,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>70000</v>
+        <v>15000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,33 +2888,33 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%243</t>
+          <t>-2.06%238</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.29%121,000</t>
+          <t>0.32%135,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>121000</v>
+        <v>135000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,33 +2949,33 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.11%87.2</t>
+          <t>+8.14%94.3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+8.14%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>87.2</v>
+        <v>94.3</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.29%339,000</t>
+          <t>0.32%378,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>339000</v>
+        <v>378000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>3406玉晶光</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.92%538</t>
+          <t>-2.11%882</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>-2.11%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>538</v>
+        <v>882</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.28%54,000</t>
+          <t>0.29%33,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>54000</v>
+        <v>33000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3406玉晶光</t>
+          <t>3044健鼎</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.44%901</t>
+          <t>-3.16%521</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-3.16%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>901</v>
+        <v>521</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.25%29,000</t>
+          <t>0.28%54,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>29000</v>
+        <v>54000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,34 +3127,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>4904遠傳</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.67%222.5</t>
+          <t>-0.95%104.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>222.5</v>
+        <v>104.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.24%110,000</t>
+          <t>0.27%266,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>110000</v>
+        <v>266000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:58</t>
+          <t>2026-09-29 22:56:36</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4904遠傳</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%105.5</t>
+          <t>-2.09%281</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>105.5</v>
+        <v>281</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.24%237,000</t>
+          <t>0.25%89,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>237000</v>
+        <v>89000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:59</t>
+          <t>2026-09-29 22:56:37</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6147頎邦</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.47%213.5</t>
+          <t>+1.57%226</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>213.5</v>
+        <v>226</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.24%113,000</t>
+          <t>0.24%110,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,11 +3276,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>113000</v>
+        <v>110000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:59</t>
+          <t>2026-09-29 22:56:37</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>6147頎邦</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+1.23%287</t>
+          <t>-2.34%208.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>287</v>
+        <v>208.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.22%80,000</t>
+          <t>0.23%113,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>80000</v>
+        <v>113000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:59</t>
+          <t>2026-09-29 22:56:37</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>2027大成鋼</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-4.06%2125</t>
+          <t>-0.95%47.15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2125</v>
+        <v>47.15</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.22%10,000</t>
+          <t>0.21%459,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>10000</v>
+        <v>459000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:59</t>
+          <t>2026-09-29 22:56:37</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2027大成鋼</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+2.15%47.6</t>
+          <t>-0.47%2115</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+2.15%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>47.6</v>
+        <v>2115</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.19%416,000</t>
+          <t>0.21%10,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>416000</v>
+        <v>10000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:59</t>
+          <t>2026-09-29 22:56:37</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,29 +3498,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-1.98%42</t>
+          <t>-1.19%41.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-1.98%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.18%429,000</t>
+          <t>0.20%487,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>429000</v>
+        <v>487000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:59</t>
+          <t>2026-09-29 22:56:37</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,29 +3559,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-0.64%1555</t>
+          <t>-2.89%1510</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1555</v>
+        <v>1510</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.15%10,000</t>
+          <t>0.17%11,000</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:59</t>
+          <t>2026-09-29 22:56:37</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-0.57%69.2</t>
+          <t>-0.72%68.7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>69.2</v>
+        <v>68.7</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:59</t>
+          <t>2026-09-29 22:56:37</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0%1305</t>
+          <t>-1.92%1280</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1305</v>
+        <v>1280</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">

--- a/etf_holdings/2026-09-29_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:34</t>
+          <t>2026-09-29 23:07:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:35</t>
+          <t>2026-09-29 23:07:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:36</t>
+          <t>2026-09-29 23:07:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:37</t>
+          <t>2026-09-29 23:07:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:37</t>
+          <t>2026-09-29 23:07:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:37</t>
+          <t>2026-09-29 23:07:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:37</t>
+          <t>2026-09-29 23:07:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:37</t>
+          <t>2026-09-29 23:07:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:37</t>
+          <t>2026-09-29 23:07:34</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:37</t>
+          <t>2026-09-29 23:07:34</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:37</t>
+          <t>2026-09-29 23:07:34</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">

--- a/etf_holdings/2026-09-29_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:31</t>
+          <t>2026-09-29 23:52:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:32</t>
+          <t>2026-09-29 23:52:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:33</t>
+          <t>2026-09-29 23:52:37</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:34</t>
+          <t>2026-09-29 23:52:38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:34</t>
+          <t>2026-09-29 23:52:38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:34</t>
+          <t>2026-09-29 23:52:38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:34</t>
+          <t>2026-09-29 23:52:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:34</t>
+          <t>2026-09-29 23:52:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:34</t>
+          <t>2026-09-29 23:52:38</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:34</t>
+          <t>2026-09-29 23:52:38</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:34</t>
+          <t>2026-09-29 23:52:38</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
